--- a/Files/RAJDHANI NIGHT.xlsx
+++ b/Files/RAJDHANI NIGHT.xlsx
@@ -10,7 +10,7 @@
     <x:sheet name="Source" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$524</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$525</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -2609,6 +2609,9 @@
   </x:si>
   <x:si>
     <x:t>24/08/2026 to 28/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31/08/2026 to 04/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>Field</x:t>
@@ -3064,7 +3067,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V524"/>
+  <x:dimension ref="A1:V525"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28.710625" style="0" customWidth="1"/>
@@ -38658,31 +38661,31 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="H524" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I524" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J524" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K524" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="L524" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="M524" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="N524" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="O524" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="P524" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="Q524" s="3" t="s">
         <x:v>37</x:v>
@@ -38703,8 +38706,76 @@
         <x:v>37</x:v>
       </x:c>
     </x:row>
+    <x:row r="525" spans="1:22">
+      <x:c r="A525" s="3" t="s">
+        <x:v>864</x:v>
+      </x:c>
+      <x:c r="B525" s="3" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="C525" s="3" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D525" s="3" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E525" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F525" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G525" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H525" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I525" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="J525" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K525" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L525" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="M525" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="N525" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="O525" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="P525" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="Q525" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="R525" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="S525" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="T525" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="U525" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="V525" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:V524"/>
+  <x:autoFilter ref="A1:V525"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -38727,39 +38798,39 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="4" t="s">
-        <x:v>864</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>865</x:v>
+        <x:v>866</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="5" t="s">
-        <x:v>866</x:v>
+        <x:v>867</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>867</x:v>
+        <x:v>868</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="5" t="s">
-        <x:v>868</x:v>
+        <x:v>869</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>869</x:v>
+        <x:v>870</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="5" t="s">
-        <x:v>870</x:v>
+        <x:v>871</x:v>
       </x:c>
       <x:c r="B4" s="6">
-        <x:v>523</x:v>
+        <x:v>524</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="5" t="s">
-        <x:v>871</x:v>
+        <x:v>872</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
         <x:v>22</x:v>
@@ -38767,10 +38838,10 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="5" t="s">
-        <x:v>872</x:v>
+        <x:v>873</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>863</x:v>
+        <x:v>864</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
